--- a/engagement_survey_forms/022_intercompany_work_allocation_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/022_intercompany_work_allocation_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -675,12 +675,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'value':_'intercompany_tasks_that_involve_communication_with_other_departments'}</t>
+          <t>intercompany_tasks_that_involve_communication_with_other_departments</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1', 'value': 'Intercompany tasks that involve communication with other departments'}</t>
+          <t>Intercompany tasks that involve communication with other departments</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'value':_'intercompany_tasks_that_involve_collaboration_with_other_teams'}</t>
+          <t>intercompany_tasks_that_involve_collaboration_with_other_teams</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2', 'value': 'Intercompany tasks that involve collaboration with other teams'}</t>
+          <t>Intercompany tasks that involve collaboration with other teams</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'value':_'intercompany_tasks_that_require_data_sharing'}</t>
+          <t>intercompany_tasks_that_require_data_sharing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3', 'value': 'Intercompany tasks that require data sharing'}</t>
+          <t>Intercompany tasks that require data sharing</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'value':_'improve_communication_between_departments'}</t>
+          <t>improve_communication_between_departments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1', 'value': 'Improve communication between departments'}</t>
+          <t>Improve communication between departments</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'value':_'increase_task_allocation_efficiency'}</t>
+          <t>increase_task_allocation_efficiency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2', 'value': 'Increase task allocation efficiency'}</t>
+          <t>Increase task allocation efficiency</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'value':_'enhance_data_sharing_practices'}</t>
+          <t>enhance_data_sharing_practices</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3', 'value': 'Enhance data sharing practices'}</t>
+          <t>Enhance data sharing practices</t>
         </is>
       </c>
     </row>
